--- a/Documents/MODULE SHEET/Module Sheet.xlsx
+++ b/Documents/MODULE SHEET/Module Sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igupta\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kdsidemo-my.sharepoint.com/personal/igupta_ironlogic_ca/Documents/Desktop/MAIN CODE/ILOps/Documents/MODULE SHEET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C16722-2597-4F76-876F-939A099B7D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{54C16722-2597-4F76-876F-939A099B7D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF5A11BA-B0A2-4AC7-91C2-B117C07A3848}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{26B0F6A5-7FA2-42B5-A050-85FFEE9A2CFB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="86">
   <si>
     <t>Remote workforce management and specialized asset tracking application that enables distributed staff to manage home-office inventory allocations, log equipment usage, and coordinate remote service dispatch.</t>
   </si>
@@ -101,27 +101,6 @@
     <t>Sales Tax Reporting (FaisalTaxReport-Spire)</t>
   </si>
   <si>
-    <t>Addresses specialized utility sector contractual rules and automated billing rate algorithms.</t>
-  </si>
-  <si>
-    <t>Manages specialized contractual utility invoicing and executes complex split payment method corrections and ledger adjustments specifically tailored for Hydro One commercial accounts in Spire.</t>
-  </si>
-  <si>
-    <t>Hydro One Fixes &amp; Billing (HydroOneFixes-Spire)</t>
-  </si>
-  <si>
-    <t>Specialized receivables accounting application providing dedicated reporting and aging delinquency analysis for outstanding commercial receivables and partner settlements within the Rogers enterprise channel.</t>
-  </si>
-  <si>
-    <t>Rogers AR Reporting (RogersAR-Spire)</t>
-  </si>
-  <si>
-    <t>Provides document extraction and batch rendering features allowing users to regenerate commercial invoices as needed, exporting formatted shipping slips and DCI/Rogers billing packages to styled PDF documents.</t>
-  </si>
-  <si>
-    <t>Output Invoices (OutputInvoices-Spire)</t>
-  </si>
-  <si>
     <t>Prevents accidental corruption of posted accounting general ledger financial totals.</t>
   </si>
   <si>
@@ -266,9 +245,6 @@
     <t>Inventory : 8 applications : 100 % code completion</t>
   </si>
   <si>
-    <t>Summary : Three Modules (Inventory, Sales, Custom Applications)</t>
-  </si>
-  <si>
     <t>Expected Time in hr.</t>
   </si>
   <si>
@@ -287,15 +263,6 @@
     <t>Requires RPT File</t>
   </si>
   <si>
-    <t>Requires template layout formatting specifications from accounting (RPT File)</t>
-  </si>
-  <si>
-    <t>Partially Pending</t>
-  </si>
-  <si>
-    <t>Console Application running behind Post Payment .</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -311,10 +278,25 @@
     <t>Module is required for core  business needs.</t>
   </si>
   <si>
-    <t>Sales : 11 applications : 45 % code completion</t>
-  </si>
-  <si>
-    <t>Custom Applications : 6 applications : To be started</t>
+    <t xml:space="preserve">Custom Applications : 6 applications : To be started </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVERALL COMPLETION : </t>
+  </si>
+  <si>
+    <t>14/25 Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary : Three Modules (Inventory, Sales, Custom Applications)  Overall Completion :14/25 Applications </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales : 11 applications : 55 % code completion ( 6 Completed,5 Pending ) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Recording  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Module on sharePoint  url  </t>
   </si>
 </sst>
 </file>
@@ -535,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -612,12 +594,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -712,19 +709,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80E872A2-89B6-4282-88C1-0364719B39E4}" name="Table1" displayName="Table1" ref="A6:J31" totalsRowShown="0">
-  <autoFilter ref="A6:J31" xr:uid="{80E872A2-89B6-4282-88C1-0364719B39E4}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{92100BC4-AF01-4BD1-8A54-ED0571EEB5F5}" name="Module Name" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{5BE9535F-3832-4865-B205-C4F77209EE7F}" name="Module Description" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{35CC8630-CB82-4258-B948-BBB3D2F83DFB}" name="Application Name" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{9947FE33-1A1C-460F-BC26-686F62192047}" name="Application Description" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{67A88265-2975-46B5-AA29-757BDA7132C8}" name="Start Date" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{77F8DBCC-D022-4194-9B1B-9EE110B3F59F}" name="Expected Dev Time in Hr" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{4BD95B18-C3F5-4BC6-BC45-3F8FA2EB9FED}" name="Completion Status" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{68F80C64-2902-49A2-B6CD-F30DC2FA161E}" name="Remarks" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{127D30A8-0DDD-4B74-BB9F-7BD8FEAE0546}" name="Dependency" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{0EACECC6-F9CF-45DB-888B-3714B79C86AF}" name="Expected Time in hr." dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80E872A2-89B6-4282-88C1-0364719B39E4}" name="Table1" displayName="Table1" ref="A7:K29" totalsRowShown="0">
+  <autoFilter ref="A7:K29" xr:uid="{80E872A2-89B6-4282-88C1-0364719B39E4}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Pending"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{92100BC4-AF01-4BD1-8A54-ED0571EEB5F5}" name="Module Name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{5BE9535F-3832-4865-B205-C4F77209EE7F}" name="Module Description" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{35CC8630-CB82-4258-B948-BBB3D2F83DFB}" name="Application Name" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{9947FE33-1A1C-460F-BC26-686F62192047}" name="Application Description" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{67A88265-2975-46B5-AA29-757BDA7132C8}" name="Start Date" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{77F8DBCC-D022-4194-9B1B-9EE110B3F59F}" name="Expected Dev Time in Hr" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{4BD95B18-C3F5-4BC6-BC45-3F8FA2EB9FED}" name="Completion Status" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{68F80C64-2902-49A2-B6CD-F30DC2FA161E}" name="Remarks" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{127D30A8-0DDD-4B74-BB9F-7BD8FEAE0546}" name="Dependency" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{0EACECC6-F9CF-45DB-888B-3714B79C86AF}" name="Expected Time in hr." dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{EB8C35DE-8D13-4668-BA01-4A0D4E55DB9B}" name="Meeting Recording  " dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1047,10 +1051,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E214E8F7-BFB5-4C50-88F2-17CF48246EF2}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
     <col min="2" max="2" width="31.26953125" customWidth="1"/>
     <col min="3" max="3" width="50.08984375" customWidth="1"/>
     <col min="4" max="4" width="31.7265625" customWidth="1"/>
@@ -1059,11 +1063,12 @@
     <col min="7" max="8" width="27" customWidth="1"/>
     <col min="9" max="9" width="18.453125" customWidth="1"/>
     <col min="10" max="10" width="19.81640625" customWidth="1"/>
+    <col min="11" max="11" width="26.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="19.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="13"/>
@@ -1074,9 +1079,9 @@
       <c r="H1" s="12"/>
       <c r="I1" s="15"/>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
@@ -1087,9 +1092,9 @@
       <c r="H2" s="17"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="18"/>
@@ -1100,9 +1105,9 @@
       <c r="H3" s="17"/>
       <c r="I3" s="20"/>
     </row>
-    <row r="4" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
@@ -1113,601 +1118,589 @@
       <c r="H4" s="23"/>
       <c r="I4" s="26"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    <row r="5" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="9" t="s">
+      <c r="B7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="137.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="6">
-        <v>46020</v>
-      </c>
-      <c r="F7" s="7">
-        <v>34.5</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="K7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="137.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E8" s="6">
-        <v>46041</v>
+        <v>46020</v>
       </c>
       <c r="F8" s="7">
-        <v>30</v>
+        <v>34.5</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" s="6">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="F9" s="7">
         <v>30</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E10" s="6">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="F10" s="7">
-        <v>67.5</v>
+        <v>30</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E11" s="6">
-        <v>46085</v>
+        <v>46065</v>
       </c>
       <c r="F11" s="7">
-        <v>47.5</v>
+        <v>67.5</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="6">
+        <v>46085</v>
+      </c>
+      <c r="F12" s="7">
+        <v>47.5</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="6">
-        <v>46100</v>
-      </c>
-      <c r="F12" s="7">
-        <v>36</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E13" s="6">
-        <v>46111</v>
+        <v>46100</v>
       </c>
       <c r="F13" s="7">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E14" s="6">
+        <v>46111</v>
+      </c>
+      <c r="F14" s="7">
+        <v>42</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="6">
         <v>46113</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F15" s="7">
         <v>48</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="G15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E16" s="6">
         <v>46120</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F16" s="7">
         <v>54</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="G16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="6">
         <v>46129</v>
-      </c>
-      <c r="F16" s="7">
-        <v>60</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="F17" s="7">
         <v>60</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>86</v>
+        <v>57</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="7">
+        <v>60</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="C19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="7">
         <v>42</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="G19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="6">
+        <v>46140</v>
+      </c>
+      <c r="F20" s="7">
+        <v>26</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="6">
+        <v>46150</v>
+      </c>
+      <c r="F21" s="7">
         <v>34</v>
       </c>
-      <c r="E19" s="6">
-        <v>46140</v>
-      </c>
-      <c r="F19" s="7">
-        <v>26</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="6">
-        <v>46150</v>
-      </c>
-      <c r="F20" s="7">
-        <v>34</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="G21" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="6">
         <v>46168</v>
-      </c>
-      <c r="F21" s="7">
-        <v>42</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="6">
-        <v>46183</v>
       </c>
       <c r="F22" s="7">
         <v>42</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E23" s="6">
-        <v>46197</v>
+        <v>46227</v>
       </c>
       <c r="F23" s="7">
         <v>42</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E24" s="6">
-        <v>46211</v>
+        <v>46230</v>
       </c>
       <c r="F24" s="7">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="6">
-        <v>46227</v>
+        <v>11</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="F25" s="7">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
@@ -1715,28 +1708,28 @@
         <v>15</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="6">
-        <v>46230</v>
+        <v>7</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="F26" s="7">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>16</v>
       </c>
@@ -1744,28 +1737,28 @@
         <v>15</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F27" s="7">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>16</v>
       </c>
@@ -1773,28 +1766,28 @@
         <v>15</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F28" s="7">
         <v>42</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>16</v>
       </c>
@@ -1802,83 +1795,69 @@
         <v>15</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F29" s="7">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" s="7">
-        <v>42</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31" s="7">
-        <v>48</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+    </row>
+    <row r="31" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+    </row>
+    <row r="32" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/MODULE SHEET/Module Sheet.xlsx
+++ b/Documents/MODULE SHEET/Module Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kdsidemo-my.sharepoint.com/personal/igupta_ironlogic_ca/Documents/Desktop/MAIN CODE/ILOps/Documents/MODULE SHEET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{54C16722-2597-4F76-876F-939A099B7D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF5A11BA-B0A2-4AC7-91C2-B117C07A3848}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{54C16722-2597-4F76-876F-939A099B7D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{285BCA5A-9FD5-4527-97B9-D501FB0E543C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{26B0F6A5-7FA2-42B5-A050-85FFEE9A2CFB}"/>
   </bookViews>
@@ -547,6 +547,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -594,18 +606,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -710,13 +710,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80E872A2-89B6-4282-88C1-0364719B39E4}" name="Table1" displayName="Table1" ref="A7:K29" totalsRowShown="0">
-  <autoFilter ref="A7:K29" xr:uid="{80E872A2-89B6-4282-88C1-0364719B39E4}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Pending"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A7:K29" xr:uid="{80E872A2-89B6-4282-88C1-0364719B39E4}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{92100BC4-AF01-4BD1-8A54-ED0571EEB5F5}" name="Module Name" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{5BE9535F-3832-4865-B205-C4F77209EE7F}" name="Module Description" dataDxfId="9"/>
@@ -1067,67 +1061,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="30"/>
     </row>
     <row r="5" spans="1:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
@@ -1175,7 +1169,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="137.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="137.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -1204,7 +1198,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1233,7 +1227,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -1262,7 +1256,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1291,7 +1285,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1320,7 +1314,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
@@ -1349,7 +1343,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1378,7 +1372,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="1" customFormat="1" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" s="1" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1407,7 +1401,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
@@ -1436,7 +1430,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
@@ -1526,7 +1520,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
@@ -1555,7 +1549,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
@@ -1584,7 +1578,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -1613,7 +1607,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="1" customFormat="1" ht="145" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" s="1" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
